--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -1202,7 +1202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N442"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -2292,403 +2292,6 @@
       <c r="F59" s="9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="60" s="6" customFormat="1"/>
-    <row r="61" s="6" customFormat="1"/>
-    <row r="62" s="6" customFormat="1"/>
-    <row r="63" s="6" customFormat="1"/>
-    <row r="64" s="6" customFormat="1"/>
-    <row r="65" s="6" customFormat="1"/>
-    <row r="66" s="6" customFormat="1"/>
-    <row r="67" s="6" customFormat="1"/>
-    <row r="68" s="6" customFormat="1"/>
-    <row r="69" s="6" customFormat="1"/>
-    <row r="70" s="6" customFormat="1"/>
-    <row r="71" s="6" customFormat="1"/>
-    <row r="72" s="6" customFormat="1"/>
-    <row r="73" s="6" customFormat="1"/>
-    <row r="74" s="6" customFormat="1"/>
-    <row r="75" s="6" customFormat="1"/>
-    <row r="76" s="6" customFormat="1"/>
-    <row r="77" s="6" customFormat="1"/>
-    <row r="78" s="6" customFormat="1"/>
-    <row r="79" s="6" customFormat="1"/>
-    <row r="80" s="6" customFormat="1"/>
-    <row r="81" s="6" customFormat="1"/>
-    <row r="82" s="6" customFormat="1"/>
-    <row r="83" s="6" customFormat="1"/>
-    <row r="84" s="6" customFormat="1"/>
-    <row r="85" s="6" customFormat="1"/>
-    <row r="86" s="6" customFormat="1"/>
-    <row r="87" s="6" customFormat="1"/>
-    <row r="88" s="6" customFormat="1"/>
-    <row r="89" s="6" customFormat="1"/>
-    <row r="90" s="6" customFormat="1"/>
-    <row r="91" s="6" customFormat="1"/>
-    <row r="92" s="6" customFormat="1"/>
-    <row r="93" s="6" customFormat="1"/>
-    <row r="94" s="6" customFormat="1"/>
-    <row r="95" s="6" customFormat="1"/>
-    <row r="96" s="6" customFormat="1"/>
-    <row r="97" s="6" customFormat="1"/>
-    <row r="98" s="6" customFormat="1"/>
-    <row r="99" s="6" customFormat="1"/>
-    <row r="100" s="6" customFormat="1"/>
-    <row r="101" s="6" customFormat="1"/>
-    <row r="102" s="6" customFormat="1"/>
-    <row r="103" s="6" customFormat="1"/>
-    <row r="104" s="6" customFormat="1"/>
-    <row r="105" s="6" customFormat="1"/>
-    <row r="106" s="6" customFormat="1"/>
-    <row r="107" s="6" customFormat="1"/>
-    <row r="108" s="6" customFormat="1"/>
-    <row r="109" s="6" customFormat="1"/>
-    <row r="110" s="6" customFormat="1"/>
-    <row r="111" s="6" customFormat="1"/>
-    <row r="112" s="6" customFormat="1"/>
-    <row r="113" s="6" customFormat="1"/>
-    <row r="114" s="6" customFormat="1"/>
-    <row r="115" s="6" customFormat="1"/>
-    <row r="116" s="6" customFormat="1"/>
-    <row r="117" s="6" customFormat="1"/>
-    <row r="118" s="6" customFormat="1"/>
-    <row r="119" s="6" customFormat="1"/>
-    <row r="120" s="6" customFormat="1"/>
-    <row r="121" s="6" customFormat="1"/>
-    <row r="122" s="6" customFormat="1"/>
-    <row r="123" s="6" customFormat="1"/>
-    <row r="124" s="6" customFormat="1"/>
-    <row r="125" s="6" customFormat="1"/>
-    <row r="126" s="6" customFormat="1"/>
-    <row r="127" s="6" customFormat="1"/>
-    <row r="128" s="6" customFormat="1"/>
-    <row r="129" s="6" customFormat="1"/>
-    <row r="130" s="6" customFormat="1"/>
-    <row r="131" s="6" customFormat="1"/>
-    <row r="132" s="6" customFormat="1"/>
-    <row r="133" s="6" customFormat="1"/>
-    <row r="134" s="6" customFormat="1"/>
-    <row r="135" s="6" customFormat="1"/>
-    <row r="136" s="6" customFormat="1"/>
-    <row r="137" s="6" customFormat="1"/>
-    <row r="138" s="6" customFormat="1"/>
-    <row r="139" s="6" customFormat="1"/>
-    <row r="140" s="6" customFormat="1"/>
-    <row r="141" s="6" customFormat="1"/>
-    <row r="142" s="6" customFormat="1"/>
-    <row r="143" s="6" customFormat="1"/>
-    <row r="144" s="6" customFormat="1"/>
-    <row r="145" s="6" customFormat="1"/>
-    <row r="146" s="6" customFormat="1"/>
-    <row r="147" s="6" customFormat="1"/>
-    <row r="148" s="6" customFormat="1"/>
-    <row r="149" s="6" customFormat="1"/>
-    <row r="150" s="6" customFormat="1"/>
-    <row r="151" s="6" customFormat="1"/>
-    <row r="152" s="6" customFormat="1"/>
-    <row r="153" s="6" customFormat="1"/>
-    <row r="154" s="6" customFormat="1"/>
-    <row r="155" s="6" customFormat="1"/>
-    <row r="156" s="6" customFormat="1"/>
-    <row r="157" s="6" customFormat="1"/>
-    <row r="158" s="6" customFormat="1"/>
-    <row r="159" s="6" customFormat="1"/>
-    <row r="160" s="6" customFormat="1"/>
-    <row r="161" s="6" customFormat="1"/>
-    <row r="162" s="6" customFormat="1"/>
-    <row r="163" s="6" customFormat="1"/>
-    <row r="164" s="6" customFormat="1"/>
-    <row r="165" s="6" customFormat="1"/>
-    <row r="166" s="6" customFormat="1"/>
-    <row r="167" s="6" customFormat="1"/>
-    <row r="168" s="6" customFormat="1"/>
-    <row r="169" s="6" customFormat="1"/>
-    <row r="170" s="6" customFormat="1"/>
-    <row r="171" s="6" customFormat="1"/>
-    <row r="172" s="6" customFormat="1"/>
-    <row r="173" s="6" customFormat="1"/>
-    <row r="174" s="6" customFormat="1"/>
-    <row r="175" s="6" customFormat="1"/>
-    <row r="176" s="6" customFormat="1"/>
-    <row r="177" s="6" customFormat="1"/>
-    <row r="178" s="6" customFormat="1"/>
-    <row r="179" s="6" customFormat="1"/>
-    <row r="180" s="6" customFormat="1"/>
-    <row r="181" s="6" customFormat="1"/>
-    <row r="182" s="6" customFormat="1"/>
-    <row r="183" s="6" customFormat="1"/>
-    <row r="184" s="6" customFormat="1"/>
-    <row r="185" s="6" customFormat="1"/>
-    <row r="186" s="6" customFormat="1"/>
-    <row r="187" s="6" customFormat="1"/>
-    <row r="188" s="6" customFormat="1"/>
-    <row r="189" s="6" customFormat="1"/>
-    <row r="190" s="6" customFormat="1"/>
-    <row r="191" s="6" customFormat="1"/>
-    <row r="192" s="6" customFormat="1"/>
-    <row r="193" s="6" customFormat="1"/>
-    <row r="194" s="6" customFormat="1"/>
-    <row r="195" s="6" customFormat="1"/>
-    <row r="196" s="6" customFormat="1"/>
-    <row r="197" s="6" customFormat="1"/>
-    <row r="198" s="6" customFormat="1"/>
-    <row r="199" s="6" customFormat="1"/>
-    <row r="200" s="6" customFormat="1"/>
-    <row r="201" s="6" customFormat="1"/>
-    <row r="202" s="6" customFormat="1"/>
-    <row r="203" s="6" customFormat="1"/>
-    <row r="204" s="6" customFormat="1"/>
-    <row r="205" s="6" customFormat="1"/>
-    <row r="206" s="6" customFormat="1"/>
-    <row r="207" s="6" customFormat="1"/>
-    <row r="208" s="6" customFormat="1"/>
-    <row r="209" s="6" customFormat="1"/>
-    <row r="210" s="6" customFormat="1"/>
-    <row r="211" s="6" customFormat="1"/>
-    <row r="212" s="6" customFormat="1"/>
-    <row r="213" s="6" customFormat="1"/>
-    <row r="214" s="6" customFormat="1"/>
-    <row r="215" s="6" customFormat="1"/>
-    <row r="216" s="6" customFormat="1"/>
-    <row r="217" s="6" customFormat="1"/>
-    <row r="218" s="6" customFormat="1"/>
-    <row r="219" s="6" customFormat="1"/>
-    <row r="220" s="6" customFormat="1"/>
-    <row r="221" s="6" customFormat="1"/>
-    <row r="222" s="6" customFormat="1"/>
-    <row r="223" s="6" customFormat="1"/>
-    <row r="224" s="6" customFormat="1"/>
-    <row r="225" s="6" customFormat="1"/>
-    <row r="226" s="6" customFormat="1"/>
-    <row r="227" s="6" customFormat="1"/>
-    <row r="228" s="6" customFormat="1"/>
-    <row r="229" s="6" customFormat="1"/>
-    <row r="230" s="6" customFormat="1"/>
-    <row r="231" s="6" customFormat="1"/>
-    <row r="232" s="6" customFormat="1"/>
-    <row r="233" s="6" customFormat="1"/>
-    <row r="234" s="6" customFormat="1"/>
-    <row r="235" s="6" customFormat="1"/>
-    <row r="236" s="6" customFormat="1"/>
-    <row r="237" s="6" customFormat="1"/>
-    <row r="238" s="6" customFormat="1"/>
-    <row r="239" s="6" customFormat="1"/>
-    <row r="240" s="6" customFormat="1"/>
-    <row r="241" s="6" customFormat="1"/>
-    <row r="242" s="6" customFormat="1"/>
-    <row r="243" s="6" customFormat="1"/>
-    <row r="244" s="6" customFormat="1"/>
-    <row r="245" s="6" customFormat="1"/>
-    <row r="246" s="6" customFormat="1"/>
-    <row r="247" s="6" customFormat="1"/>
-    <row r="248" s="6" customFormat="1"/>
-    <row r="249" s="6" customFormat="1"/>
-    <row r="250" s="6" customFormat="1"/>
-    <row r="251" s="6" customFormat="1"/>
-    <row r="252" s="6" customFormat="1"/>
-    <row r="253" s="6" customFormat="1"/>
-    <row r="254" s="6" customFormat="1"/>
-    <row r="255" s="6" customFormat="1"/>
-    <row r="256" s="6" customFormat="1"/>
-    <row r="257" s="6" customFormat="1"/>
-    <row r="258" s="6" customFormat="1"/>
-    <row r="259" s="6" customFormat="1"/>
-    <row r="260" s="6" customFormat="1"/>
-    <row r="261" s="6" customFormat="1"/>
-    <row r="262" s="6" customFormat="1"/>
-    <row r="263" s="6" customFormat="1"/>
-    <row r="264" s="6" customFormat="1"/>
-    <row r="265" s="6" customFormat="1"/>
-    <row r="266" s="6" customFormat="1"/>
-    <row r="267" s="6" customFormat="1"/>
-    <row r="268" s="6" customFormat="1"/>
-    <row r="269" s="6" customFormat="1"/>
-    <row r="270" s="6" customFormat="1"/>
-    <row r="271" s="6" customFormat="1"/>
-    <row r="272" s="6" customFormat="1"/>
-    <row r="273" s="6" customFormat="1"/>
-    <row r="274" s="6" customFormat="1"/>
-    <row r="275" s="6" customFormat="1"/>
-    <row r="276" s="6" customFormat="1"/>
-    <row r="277" s="6" customFormat="1"/>
-    <row r="278" s="6" customFormat="1"/>
-    <row r="279" s="6" customFormat="1"/>
-    <row r="280" s="6" customFormat="1"/>
-    <row r="281" s="6" customFormat="1"/>
-    <row r="282" s="6" customFormat="1"/>
-    <row r="283" s="6" customFormat="1"/>
-    <row r="284" s="6" customFormat="1"/>
-    <row r="285" s="6" customFormat="1"/>
-    <row r="286" s="6" customFormat="1"/>
-    <row r="287" s="6" customFormat="1"/>
-    <row r="288" s="6" customFormat="1"/>
-    <row r="289" s="6" customFormat="1"/>
-    <row r="290" s="6" customFormat="1"/>
-    <row r="291" s="6" customFormat="1"/>
-    <row r="292" s="6" customFormat="1"/>
-    <row r="293" s="6" customFormat="1"/>
-    <row r="294" s="6" customFormat="1"/>
-    <row r="295" s="6" customFormat="1"/>
-    <row r="296" s="6" customFormat="1"/>
-    <row r="297" s="6" customFormat="1"/>
-    <row r="298" s="6" customFormat="1"/>
-    <row r="299" s="6" customFormat="1"/>
-    <row r="300" s="6" customFormat="1"/>
-    <row r="301" s="6" customFormat="1"/>
-    <row r="302" s="6" customFormat="1"/>
-    <row r="303" s="6" customFormat="1"/>
-    <row r="304" s="6" customFormat="1"/>
-    <row r="305" s="6" customFormat="1"/>
-    <row r="306" s="6" customFormat="1"/>
-    <row r="307" s="6" customFormat="1"/>
-    <row r="308" s="6" customFormat="1"/>
-    <row r="309" s="6" customFormat="1"/>
-    <row r="310" s="6" customFormat="1"/>
-    <row r="311" s="6" customFormat="1"/>
-    <row r="312" s="6" customFormat="1"/>
-    <row r="313" s="6" customFormat="1"/>
-    <row r="314" s="6" customFormat="1"/>
-    <row r="315" s="6" customFormat="1"/>
-    <row r="316" s="6" customFormat="1"/>
-    <row r="317" s="6" customFormat="1"/>
-    <row r="318" s="6" customFormat="1"/>
-    <row r="319" s="6" customFormat="1"/>
-    <row r="320" s="6" customFormat="1"/>
-    <row r="321" s="6" customFormat="1"/>
-    <row r="322" s="6" customFormat="1"/>
-    <row r="323" s="6" customFormat="1"/>
-    <row r="324" s="6" customFormat="1"/>
-    <row r="325" s="6" customFormat="1"/>
-    <row r="326" s="6" customFormat="1"/>
-    <row r="327" s="6" customFormat="1"/>
-    <row r="328" s="6" customFormat="1"/>
-    <row r="329" s="6" customFormat="1"/>
-    <row r="330" s="6" customFormat="1"/>
-    <row r="331" s="6" customFormat="1"/>
-    <row r="332" s="6" customFormat="1"/>
-    <row r="333" s="6" customFormat="1"/>
-    <row r="334" s="6" customFormat="1"/>
-    <row r="335" s="6" customFormat="1"/>
-    <row r="336" s="6" customFormat="1"/>
-    <row r="337" s="6" customFormat="1"/>
-    <row r="338" s="6" customFormat="1"/>
-    <row r="339" s="6" customFormat="1"/>
-    <row r="340" s="6" customFormat="1"/>
-    <row r="341" s="6" customFormat="1"/>
-    <row r="342" s="6" customFormat="1"/>
-    <row r="343" s="6" customFormat="1"/>
-    <row r="344" s="6" customFormat="1"/>
-    <row r="345" s="6" customFormat="1"/>
-    <row r="346" s="6" customFormat="1"/>
-    <row r="347" s="6" customFormat="1"/>
-    <row r="348" s="6" customFormat="1"/>
-    <row r="349" s="6" customFormat="1"/>
-    <row r="350" s="6" customFormat="1"/>
-    <row r="351" s="6" customFormat="1"/>
-    <row r="352" s="6" customFormat="1"/>
-    <row r="353" s="6" customFormat="1"/>
-    <row r="354" s="6" customFormat="1"/>
-    <row r="355" s="6" customFormat="1"/>
-    <row r="356" s="6" customFormat="1"/>
-    <row r="357" s="6" customFormat="1"/>
-    <row r="358" s="6" customFormat="1"/>
-    <row r="359" s="6" customFormat="1"/>
-    <row r="360" s="6" customFormat="1"/>
-    <row r="361" s="6" customFormat="1"/>
-    <row r="362" s="6" customFormat="1"/>
-    <row r="363" s="6" customFormat="1"/>
-    <row r="364" s="6" customFormat="1"/>
-    <row r="365" s="6" customFormat="1"/>
-    <row r="366" s="6" customFormat="1"/>
-    <row r="367" s="6" customFormat="1"/>
-    <row r="368" s="6" customFormat="1"/>
-    <row r="369" s="6" customFormat="1"/>
-    <row r="370" s="6" customFormat="1"/>
-    <row r="371" s="6" customFormat="1"/>
-    <row r="372" s="6" customFormat="1"/>
-    <row r="373" s="6" customFormat="1"/>
-    <row r="374" s="6" customFormat="1"/>
-    <row r="375" s="6" customFormat="1"/>
-    <row r="376" s="6" customFormat="1"/>
-    <row r="377" s="6" customFormat="1"/>
-    <row r="378" s="6" customFormat="1"/>
-    <row r="379" s="6" customFormat="1"/>
-    <row r="380" s="6" customFormat="1"/>
-    <row r="381" s="6" customFormat="1"/>
-    <row r="382" s="6" customFormat="1"/>
-    <row r="383" s="6" customFormat="1"/>
-    <row r="384" s="6" customFormat="1"/>
-    <row r="385" s="6" customFormat="1"/>
-    <row r="386" s="6" customFormat="1"/>
-    <row r="387" s="6" customFormat="1"/>
-    <row r="388" s="6" customFormat="1"/>
-    <row r="389" s="6" customFormat="1"/>
-    <row r="390" s="6" customFormat="1"/>
-    <row r="391" s="6" customFormat="1"/>
-    <row r="392" s="6" customFormat="1"/>
-    <row r="393" s="6" customFormat="1"/>
-    <row r="394" s="6" customFormat="1"/>
-    <row r="395" s="6" customFormat="1"/>
-    <row r="396" s="6" customFormat="1"/>
-    <row r="397" s="6" customFormat="1"/>
-    <row r="398" s="6" customFormat="1"/>
-    <row r="399" s="6" customFormat="1"/>
-    <row r="400" s="6" customFormat="1"/>
-    <row r="401" s="6" customFormat="1"/>
-    <row r="402" s="6" customFormat="1"/>
-    <row r="403" s="6" customFormat="1"/>
-    <row r="404" s="6" customFormat="1"/>
-    <row r="405" s="6" customFormat="1"/>
-    <row r="406" s="6" customFormat="1"/>
-    <row r="407" s="6" customFormat="1"/>
-    <row r="408" s="6" customFormat="1"/>
-    <row r="409" s="6" customFormat="1"/>
-    <row r="410" s="6" customFormat="1"/>
-    <row r="411" s="6" customFormat="1"/>
-    <row r="412" s="6" customFormat="1"/>
-    <row r="413" s="6" customFormat="1"/>
-    <row r="414" s="6" customFormat="1"/>
-    <row r="415" s="6" customFormat="1"/>
-    <row r="416" s="6" customFormat="1"/>
-    <row r="417" s="6" customFormat="1"/>
-    <row r="418" s="6" customFormat="1"/>
-    <row r="419" s="6" customFormat="1"/>
-    <row r="420" s="6" customFormat="1"/>
-    <row r="421" s="6" customFormat="1"/>
-    <row r="422" s="6" customFormat="1"/>
-    <row r="423" s="6" customFormat="1"/>
-    <row r="424" s="6" customFormat="1"/>
-    <row r="425" s="6" customFormat="1"/>
-    <row r="426" s="6" customFormat="1"/>
-    <row r="427" s="6" customFormat="1"/>
-    <row r="428" s="6" customFormat="1"/>
-    <row r="429" s="6" customFormat="1"/>
-    <row r="430" s="6" customFormat="1"/>
-    <row r="431" s="6" customFormat="1"/>
-    <row r="432" s="6" customFormat="1"/>
-    <row r="433" s="6" customFormat="1"/>
-    <row r="434" s="6" customFormat="1"/>
-    <row r="435" s="6" customFormat="1"/>
-    <row r="436" s="6" customFormat="1"/>
-    <row r="437" s="6" customFormat="1"/>
-    <row r="438" s="6" customFormat="1"/>
-    <row r="439" s="6" customFormat="1"/>
-    <row r="440" s="6" customFormat="1"/>
-    <row r="441" s="6" customFormat="1" spans="2:7">
-      <c r="B441" s="10"/>
-      <c r="C441" s="9"/>
-      <c r="D441" s="9"/>
-      <c r="E441" s="9"/>
-      <c r="F441" s="9"/>
-      <c r="G441" s="9"/>
-    </row>
-    <row r="442" s="6" customFormat="1" spans="2:7">
-      <c r="B442" s="10"/>
-      <c r="C442" s="9"/>
-      <c r="D442" s="9"/>
-      <c r="E442" s="9"/>
-      <c r="F442" s="9"/>
-      <c r="G442" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -95,54 +95,12 @@
     <t>DBCache</t>
   </si>
   <si>
-    <t>Chat</t>
-  </si>
-  <si>
-    <t>EMail</t>
-  </si>
-  <si>
-    <t>Activity</t>
-  </si>
-  <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>PaiMai</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Friend</t>
-  </si>
-  <si>
-    <t>Union</t>
-  </si>
-  <si>
     <t>Map</t>
   </si>
   <si>
     <t>Map101</t>
   </si>
   <si>
-    <t>JiaYuan</t>
-  </si>
-  <si>
-    <t>Popularize</t>
-  </si>
-  <si>
-    <t>Solo</t>
-  </si>
-  <si>
-    <t>FubenCenter</t>
-  </si>
-  <si>
-    <t>FubenCenter1</t>
-  </si>
-  <si>
-    <t>FubenCenter2</t>
-  </si>
-  <si>
     <t>LoginCenter</t>
   </si>
   <si>
@@ -150,9 +108,6 @@
   </si>
   <si>
     <t>Location</t>
-  </si>
-  <si>
-    <t>ReCharge</t>
   </si>
   <si>
     <t>RobotManager</t>
@@ -1202,8 +1157,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="10" customWidth="1"/>
@@ -1282,8 +1237,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" s="5" customFormat="1" spans="1:14">
-      <c r="A4" s="6"/>
+    <row r="4" s="5" customFormat="1" spans="2:7">
       <c r="B4" s="12">
         <v>101</v>
       </c>
@@ -1302,15 +1256,8 @@
       <c r="G4" s="9">
         <v>30325</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" s="5" customFormat="1" spans="2:14">
+    </row>
+    <row r="5" s="5" customFormat="1" spans="2:7">
       <c r="B5" s="12">
         <v>102</v>
       </c>
@@ -1329,15 +1276,8 @@
       <c r="G5" s="8">
         <v>30326</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" s="5" customFormat="1" spans="2:14">
+    </row>
+    <row r="6" s="5" customFormat="1" spans="2:7">
       <c r="B6" s="12">
         <v>103</v>
       </c>
@@ -1356,13 +1296,6 @@
       <c r="G6" s="9">
         <v>30327</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="12">
@@ -1383,914 +1316,19 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="12">
-        <v>105</v>
-      </c>
-      <c r="C8" s="8">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
+        <v>113</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
         <v>1</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="12">
-        <v>106</v>
-      </c>
-      <c r="C9" s="9">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="12">
-        <v>107</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="12">
-        <v>108</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="12">
-        <v>109</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="12">
-        <v>110</v>
-      </c>
-      <c r="C13" s="8">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="12">
-        <v>111</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="12">
-        <v>112</v>
-      </c>
-      <c r="C15" s="9">
-        <v>1</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="12">
-        <v>113</v>
-      </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="12">
-        <v>114</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="12">
-        <v>115</v>
-      </c>
-      <c r="C18" s="9">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6">
-      <c r="B19" s="12">
-        <v>116</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9">
-        <v>1</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6">
-      <c r="B20" s="12">
-        <v>117</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8">
-        <v>1</v>
-      </c>
-      <c r="E20" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6">
-      <c r="B21" s="12">
-        <v>118</v>
-      </c>
-      <c r="C21" s="8">
-        <v>1</v>
-      </c>
-      <c r="D21" s="8">
-        <v>1</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4">
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="12">
-        <v>201</v>
-      </c>
-      <c r="C23" s="8">
-        <v>2</v>
-      </c>
-      <c r="D23" s="8">
-        <v>1</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" s="9">
-        <v>20335</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12">
-        <v>202</v>
-      </c>
-      <c r="C24" s="8">
-        <v>2</v>
-      </c>
-      <c r="D24" s="8">
-        <v>1</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="8">
-        <v>20336</v>
-      </c>
-    </row>
-    <row r="25" s="6" customFormat="1" spans="1:7">
-      <c r="A25" s="5"/>
-      <c r="B25" s="12">
-        <v>203</v>
-      </c>
-      <c r="C25" s="9">
-        <v>2</v>
-      </c>
-      <c r="D25" s="9">
-        <v>1</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="9">
-        <v>20337</v>
-      </c>
-    </row>
-    <row r="26" s="6" customFormat="1" spans="2:7">
-      <c r="B26" s="12">
-        <v>204</v>
-      </c>
-      <c r="C26" s="8">
-        <v>2</v>
-      </c>
-      <c r="D26" s="8">
-        <v>1</v>
-      </c>
-      <c r="E26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" s="6" customFormat="1" spans="2:7">
-      <c r="B27" s="12">
-        <v>205</v>
-      </c>
-      <c r="C27" s="8">
-        <v>2</v>
-      </c>
-      <c r="D27" s="8">
-        <v>1</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="9"/>
-    </row>
-    <row r="28" s="6" customFormat="1" spans="2:7">
-      <c r="B28" s="12">
-        <v>206</v>
-      </c>
-      <c r="C28" s="9">
-        <v>2</v>
-      </c>
-      <c r="D28" s="8">
-        <v>1</v>
-      </c>
-      <c r="E28" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" s="6" customFormat="1" spans="2:7">
-      <c r="B29" s="12">
-        <v>207</v>
-      </c>
-      <c r="C29" s="8">
-        <v>2</v>
-      </c>
-      <c r="D29" s="9">
-        <v>1</v>
-      </c>
-      <c r="E29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" s="6" customFormat="1" spans="2:7">
-      <c r="B30" s="12">
-        <v>208</v>
-      </c>
-      <c r="C30" s="8">
-        <v>2</v>
-      </c>
-      <c r="D30" s="8">
-        <v>1</v>
-      </c>
-      <c r="E30" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" s="6" customFormat="1" spans="2:7">
-      <c r="B31" s="12">
-        <v>209</v>
-      </c>
-      <c r="C31" s="9">
-        <v>2</v>
-      </c>
-      <c r="D31" s="8">
-        <v>1</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" s="6" customFormat="1" spans="2:7">
-      <c r="B32" s="12">
-        <v>210</v>
-      </c>
-      <c r="C32" s="8">
-        <v>2</v>
-      </c>
-      <c r="D32" s="8">
-        <v>1</v>
-      </c>
-      <c r="E32" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" s="6" customFormat="1" spans="2:7">
-      <c r="B33" s="12">
-        <v>211</v>
-      </c>
-      <c r="C33" s="8">
-        <v>2</v>
-      </c>
-      <c r="D33" s="9">
-        <v>1</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" s="6" customFormat="1" spans="2:7">
-      <c r="B34" s="12">
-        <v>212</v>
-      </c>
-      <c r="C34" s="9">
-        <v>2</v>
-      </c>
-      <c r="D34" s="8">
-        <v>1</v>
-      </c>
-      <c r="E34" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" s="6" customFormat="1" spans="2:7">
-      <c r="B35" s="12">
-        <v>213</v>
-      </c>
-      <c r="C35" s="8">
-        <v>2</v>
-      </c>
-      <c r="D35" s="9">
-        <v>1</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" s="6" customFormat="1" spans="2:7">
-      <c r="B36" s="12">
-        <v>214</v>
-      </c>
-      <c r="C36" s="8">
-        <v>2</v>
-      </c>
-      <c r="D36" s="8">
-        <v>1</v>
-      </c>
-      <c r="E36" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" s="6" customFormat="1" spans="2:7">
-      <c r="B37" s="12">
-        <v>215</v>
-      </c>
-      <c r="C37" s="9">
-        <v>2</v>
-      </c>
-      <c r="D37" s="8">
-        <v>1</v>
-      </c>
-      <c r="E37" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" s="6" customFormat="1" spans="2:7">
-      <c r="B38" s="12">
-        <v>216</v>
-      </c>
-      <c r="C38" s="8">
-        <v>2</v>
-      </c>
-      <c r="D38" s="9">
-        <v>1</v>
-      </c>
-      <c r="E38" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" s="6" customFormat="1" spans="2:7">
-      <c r="B39" s="12">
-        <v>217</v>
-      </c>
-      <c r="C39" s="8">
-        <v>2</v>
-      </c>
-      <c r="D39" s="8">
-        <v>1</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" s="6" customFormat="1" spans="2:6">
-      <c r="B40" s="12">
-        <v>218</v>
-      </c>
-      <c r="C40" s="9">
-        <v>2</v>
-      </c>
-      <c r="D40" s="8">
-        <v>1</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="41" s="6" customFormat="1" spans="2:6">
-      <c r="B41" s="12"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" s="6" customFormat="1" spans="2:7">
-      <c r="B42" s="12">
-        <v>301</v>
-      </c>
-      <c r="C42" s="8">
-        <v>3</v>
-      </c>
-      <c r="D42" s="8">
-        <v>1</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G42" s="9">
-        <v>20345</v>
-      </c>
-    </row>
-    <row r="43" s="6" customFormat="1" spans="1:7">
-      <c r="A43" s="5"/>
-      <c r="B43" s="12">
-        <v>302</v>
-      </c>
-      <c r="C43" s="8">
-        <v>3</v>
-      </c>
-      <c r="D43" s="8">
-        <v>1</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G43" s="8">
-        <v>20346</v>
-      </c>
-    </row>
-    <row r="44" s="6" customFormat="1" spans="1:7">
-      <c r="A44" s="5"/>
-      <c r="B44" s="12">
-        <v>303</v>
-      </c>
-      <c r="C44" s="8">
-        <v>3</v>
-      </c>
-      <c r="D44" s="9">
-        <v>1</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="9">
-        <v>20347</v>
-      </c>
-    </row>
-    <row r="45" s="6" customFormat="1" spans="2:7">
-      <c r="B45" s="12">
-        <v>304</v>
-      </c>
-      <c r="C45" s="8">
-        <v>3</v>
-      </c>
-      <c r="D45" s="8">
-        <v>1</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" s="9"/>
-    </row>
-    <row r="46" s="6" customFormat="1" spans="2:7">
-      <c r="B46" s="12">
-        <v>305</v>
-      </c>
-      <c r="C46" s="8">
-        <v>3</v>
-      </c>
-      <c r="D46" s="8">
-        <v>1</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" s="6" customFormat="1" spans="2:7">
-      <c r="B47" s="12">
-        <v>306</v>
-      </c>
-      <c r="C47" s="8">
-        <v>3</v>
-      </c>
-      <c r="D47" s="8">
-        <v>1</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G47" s="9"/>
-    </row>
-    <row r="48" s="6" customFormat="1" spans="2:7">
-      <c r="B48" s="12">
-        <v>307</v>
-      </c>
-      <c r="C48" s="8">
-        <v>3</v>
-      </c>
-      <c r="D48" s="9">
-        <v>1</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" s="6" customFormat="1" spans="2:7">
-      <c r="B49" s="12">
-        <v>308</v>
-      </c>
-      <c r="C49" s="8">
-        <v>3</v>
-      </c>
-      <c r="D49" s="8">
-        <v>1</v>
-      </c>
-      <c r="E49" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" s="6" customFormat="1" spans="2:7">
-      <c r="B50" s="12">
-        <v>309</v>
-      </c>
-      <c r="C50" s="8">
-        <v>3</v>
-      </c>
-      <c r="D50" s="8">
-        <v>1</v>
-      </c>
-      <c r="E50" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" s="9"/>
-    </row>
-    <row r="51" s="6" customFormat="1" ht="13.5" customHeight="1" spans="2:7">
-      <c r="B51" s="12">
-        <v>310</v>
-      </c>
-      <c r="C51" s="8">
-        <v>3</v>
-      </c>
-      <c r="D51" s="8">
-        <v>1</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="9"/>
-    </row>
-    <row r="52" s="6" customFormat="1" spans="2:7">
-      <c r="B52" s="12">
-        <v>311</v>
-      </c>
-      <c r="C52" s="8">
-        <v>3</v>
-      </c>
-      <c r="D52" s="9">
-        <v>1</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G52" s="9"/>
-    </row>
-    <row r="53" s="6" customFormat="1" spans="2:7">
-      <c r="B53" s="12">
-        <v>312</v>
-      </c>
-      <c r="C53" s="8">
-        <v>3</v>
-      </c>
-      <c r="D53" s="8">
-        <v>1</v>
-      </c>
-      <c r="E53" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F53" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="G53" s="9"/>
-    </row>
-    <row r="54" s="6" customFormat="1" spans="2:7">
-      <c r="B54" s="12">
-        <v>313</v>
-      </c>
-      <c r="C54" s="8">
-        <v>3</v>
-      </c>
-      <c r="D54" s="9">
-        <v>1</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G54" s="9"/>
-    </row>
-    <row r="55" s="6" customFormat="1" spans="2:7">
-      <c r="B55" s="12">
-        <v>314</v>
-      </c>
-      <c r="C55" s="8">
-        <v>3</v>
-      </c>
-      <c r="D55" s="8">
-        <v>1</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="G55" s="9"/>
-    </row>
-    <row r="56" s="6" customFormat="1" spans="2:7">
-      <c r="B56" s="12">
-        <v>315</v>
-      </c>
-      <c r="C56" s="8">
-        <v>3</v>
-      </c>
-      <c r="D56" s="8">
-        <v>1</v>
-      </c>
-      <c r="E56" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F56" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G56" s="9"/>
-    </row>
-    <row r="57" s="6" customFormat="1" spans="2:7">
-      <c r="B57" s="12">
-        <v>316</v>
-      </c>
-      <c r="C57" s="8">
-        <v>3</v>
-      </c>
-      <c r="D57" s="9">
-        <v>1</v>
-      </c>
-      <c r="E57" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F57" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G57" s="9"/>
-    </row>
-    <row r="58" s="6" customFormat="1" spans="2:7">
-      <c r="B58" s="12">
-        <v>317</v>
-      </c>
-      <c r="C58" s="8">
-        <v>3</v>
-      </c>
-      <c r="D58" s="8">
-        <v>1</v>
-      </c>
-      <c r="E58" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F58" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G58" s="9"/>
-    </row>
-    <row r="59" s="6" customFormat="1" spans="2:6">
-      <c r="B59" s="12">
-        <v>318</v>
-      </c>
-      <c r="C59" s="8">
-        <v>3</v>
-      </c>
-      <c r="D59" s="8">
-        <v>1</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2303,8 +1341,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="10.25" customWidth="1"/>
     <col min="5" max="5" width="15.75" customWidth="1"/>
@@ -2391,10 +1429,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -2411,10 +1449,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -2431,29 +1469,12 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G6" s="8"/>
-    </row>
-    <row r="7" ht="14.25" spans="2:6">
-      <c r="B7" s="8">
-        <v>1000204</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2553,10 +1574,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -2658,7 +1679,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:7">
+    <row r="3" customFormat="1" ht="14.25" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2693,10 +1714,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -2714,10 +1735,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -2735,10 +1756,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -2756,10 +1777,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -2777,10 +1798,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="12960"/>
   </bookViews>
   <sheets>
     <sheet name="StartSceneConfig" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="34">
   <si>
     <t>##var</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Map101</t>
+  </si>
+  <si>
+    <t>Mail</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1157,8 +1160,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="10" customWidth="1"/>
@@ -1329,6 +1332,23 @@
       </c>
       <c r="F8" s="9" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="10">
+        <v>114</v>
+      </c>
+      <c r="C9" s="9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1429,10 +1449,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1449,10 +1469,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1469,10 +1489,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1574,10 +1594,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1714,10 +1734,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1735,10 +1755,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1756,10 +1776,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1777,10 +1797,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1798,10 +1818,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Mail</t>
+  </si>
+  <si>
+    <t>Chat</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1160,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1349,6 +1352,23 @@
       </c>
       <c r="F9" s="9" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="10">
+        <v>115</v>
+      </c>
+      <c r="C10" s="9">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1449,10 +1469,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1469,10 +1489,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1489,10 +1509,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1594,10 +1614,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1734,10 +1754,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1755,10 +1775,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1776,10 +1796,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1797,10 +1817,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1818,10 +1838,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Chat</t>
+  </si>
+  <si>
+    <t>Friend</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1163,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1369,6 +1372,23 @@
       </c>
       <c r="F10" s="9" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="10">
+        <v>116</v>
+      </c>
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1469,10 +1489,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1489,10 +1509,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1509,10 +1529,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1614,10 +1634,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1754,10 +1774,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1775,10 +1795,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1796,10 +1816,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1817,10 +1837,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1838,10 +1858,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="37">
   <si>
     <t>##var</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Friend</t>
+  </si>
+  <si>
+    <t>Center</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1166,7 +1169,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1389,6 +1392,23 @@
       </c>
       <c r="F11" s="9" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="10">
+        <v>117</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1489,10 +1509,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1509,10 +1529,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1529,10 +1549,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1634,10 +1654,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1774,10 +1794,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1795,10 +1815,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1816,10 +1836,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1837,10 +1857,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1858,10 +1878,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Center</t>
+  </si>
+  <si>
+    <t>Rank</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1169,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1409,6 +1412,23 @@
       </c>
       <c r="F12" s="9" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="10">
+        <v>118</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1509,10 +1529,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1529,10 +1549,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1549,10 +1569,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1654,10 +1674,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1794,10 +1814,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1815,10 +1835,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1836,10 +1856,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1857,10 +1877,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1878,10 +1898,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>

--- a/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
+++ b/Unity/Assets/Config/Excel/StartConfig/Release/StartSceneConfig.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Rank</t>
+  </si>
+  <si>
+    <t>Alliance</t>
   </si>
   <si>
     <t>LoginCenter</t>
@@ -1172,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12.75" style="6" customWidth="1"/>
@@ -1429,6 +1432,23 @@
       </c>
       <c r="F13" s="9" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="10">
+        <v>119</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1529,10 +1549,10 @@
         <v>1000</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G4" s="8">
         <v>30310</v>
@@ -1549,10 +1569,10 @@
         <v>1000</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8">
         <v>30311</v>
@@ -1569,10 +1589,10 @@
         <v>1000</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -1674,10 +1694,10 @@
         <v>1001</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -1814,10 +1834,10 @@
         <v>1002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4" s="4">
         <v>30300</v>
@@ -1835,10 +1855,10 @@
         <v>1002</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G5" s="4">
         <v>30301</v>
@@ -1856,10 +1876,10 @@
         <v>1002</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="4">
         <v>30302</v>
@@ -1877,10 +1897,10 @@
         <v>1002</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="4">
         <v>30303</v>
@@ -1898,10 +1918,10 @@
         <v>1002</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="4">
         <v>30304</v>
